--- a/news_daily/2026-09-28.xlsx
+++ b/news_daily/2026-09-28.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,10 +92,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -991,6 +1015,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1161,6 +1189,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1331,6 +1363,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1366,28 +1402,32 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1427,7 +1467,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1436,7 +1476,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>ad24e6be1d7c42b8bb6df1c5b9d33101</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>1d4457fb5b4b603d601d65c9</t>
@@ -1457,7 +1501,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1501,176 +1549,216 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>FTC Settlement Limits Corteva Pesticide Loyalty Rebates</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.341</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>The Scoop -</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>c01631ea0f5c4f07b67037d7c8c17767</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>58e4a361c64031ce84799cb6</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>2dd32bc16b9d7b34926af28d</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.341</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The Scoop -</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>58e4a361c64031ce84799cb6</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>2dd32bc16b9d7b34926af28d</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1841,346 +1929,398 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Corteva to End Pesticides Loyalty Program in Settlement With FTC</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.303</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>11716aa49bca4ff88bcc87ed06b74273</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>854069c078ef7dea44692cfc</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>96db35c9ac23729f442bd528</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.303</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>854069c078ef7dea44692cfc</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>96db35c9ac23729f442bd528</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Corteva reaches FTC antitrust settlement, agrees to $35M payment (CTVA:NYSE)</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>67911ce819d3444591d6976b52d3134f</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>4b033dbf29afc311be67812a</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>add022a25ab732e3141ba5e8</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>4b033dbf29afc311be67812a</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>add022a25ab732e3141ba5e8</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2216,28 +2356,32 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2277,7 +2421,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -2286,7 +2430,11 @@
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>cfe9a633a44a4d83a1a210ee983786cd</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
           <t>7e5c915e760701c5b0c0bd28</t>
@@ -2307,7 +2455,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -2343,176 +2495,216 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>States, FTC secure settlement in suit against Corteva pesticide loyalty programs</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Iowa Capital Dispatch</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>2aacab99b13e4da492dd8f89a9d0ccb6</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>fa55d6f911a75d41e6f1ed9e</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>ef1fdace1b4d4ef928a14b4d</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Iowa Capital Dispatch</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>fa55d6f911a75d41e6f1ed9e</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>ef1fdace1b4d4ef928a14b4d</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2548,28 +2740,32 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2609,7 +2805,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2618,7 +2814,11 @@
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>8fee310a77674df0a73f9e3870b6236f</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>eba33791b81f597b4205d71a</t>
@@ -2639,7 +2839,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -2683,6 +2887,22 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2718,28 +2938,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2779,7 +3003,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -2788,7 +3012,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>f0d4bf2d2b994dc1b1ba1a80292aa45b</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>fb8abff601832e31f53924b5</t>
@@ -2809,7 +3037,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -2845,6 +3077,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2880,28 +3128,32 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -2941,7 +3193,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2950,7 +3202,11 @@
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>e15cfa024e314823a07a6d3c033d3a41</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>883f49f228b9610ccb17dbef</t>
@@ -2971,7 +3227,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3007,6 +3267,22 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3042,28 +3318,32 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3103,7 +3383,7 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -3112,7 +3392,11 @@
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>f0711541479e401c9c83cd2d1b80d367</t>
+        </is>
+      </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>2a6cdf6613b7924e2889db28</t>
@@ -3133,7 +3417,11 @@
       <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="inlineStr"/>
       <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="3" t="inlineStr"/>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
@@ -3169,6 +3457,22 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3339,168 +3643,196 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>PNR DEADLINE NOTICE: Faruqi &amp; Faruqi, LLP Reminds Pentair (PNR) Investors of Securities Class Action Lawsuit Deadline on October 2, 2026</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>'-0.068</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>f1d55caddc654688b58c6fb579b28c84</t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>e219e320bea4f382169bc711</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>3b46f49745e60c6b38e6f5c0</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr"/>
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
-        <is>
-          <t>e219e320bea4f382169bc711</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>3b46f49745e60c6b38e6f5c0</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr"/>
+      <c r="AS17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr"/>
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC17" s="3" t="inlineStr">
+      <c r="BC17" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr">
+      <c r="BD17" s="4" t="inlineStr"/>
+      <c r="BE17" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr">
+      <c r="BF17" s="4" t="inlineStr"/>
+      <c r="BG17" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr"/>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3536,28 +3868,32 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -3597,7 +3933,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -3606,7 +3942,11 @@
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>fb3cbda1c08d4432a26eb521753d031c</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
           <t>a5d0531db2cabc233a69b07d</t>
@@ -3627,7 +3967,11 @@
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="3" t="inlineStr"/>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
@@ -3671,689 +4015,721 @@
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>SA analyst upgrades/downgrades: AAPL, IBM, UBER, HOG (IBM:NYSE)</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>'-0.428</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNY2pHXzZ0YWdQSFF1ODROWnRlN0I4YVdlTjBsWFVoVkVYZ0dsd0hkS25QbmxCakZpNHhPQWxMZ3Vxc3ZrSFQ1SnJYTXpoNmI2R0wyY2JfOTR0OGRqSDhLV3ZGVGRLZXc0TzVSVzlvTnRMbnE5OENEbXZ4YkxWajROSXhYekVPSl9DWjV4amZB?oc=5</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr">
+      <c r="V19" s="3" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
+      <c r="W19" s="3" t="inlineStr"/>
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y19" s="4" t="inlineStr">
+      <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
         </is>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AD19" s="3" t="inlineStr">
         <is>
           <t>66e36ff245e18d26ca3537a8</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr">
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr"/>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
+      <c r="AX19" s="3" t="inlineStr"/>
+      <c r="AY19" s="3" t="inlineStr"/>
+      <c r="AZ19" s="3" t="inlineStr"/>
+      <c r="BA19" s="3" t="inlineStr"/>
+      <c r="BB19" s="3" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC19" s="4" t="inlineStr">
+      <c r="BC19" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
+      <c r="BD19" s="3" t="inlineStr"/>
+      <c r="BE19" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF19" s="4" t="inlineStr">
+      <c r="BF19" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG19" s="4" t="inlineStr">
+      <c r="BG19" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BH19" s="3" t="inlineStr"/>
+      <c r="BI19" s="3" t="inlineStr"/>
+      <c r="BJ19" s="3" t="inlineStr"/>
+      <c r="BK19" s="3" t="inlineStr"/>
+      <c r="BL19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>ADI</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Analog Devices, Inc.</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>ADI Global Distribution Shares Fall After Evercore ISI Initiates With In Line Rating</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>'-0.95</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOR2hFZHhDaWRUSVBNeXRURGpaRUNDY1BFRC1kQkFhbGxSb2NEQWhZbENCcjZPOUYzdXJqanVLQXZOTnNmT25NTG1PX3lKYVNSc3dUbUllX3FybFdqa3FlR05HSnhUR1N0UEJLVzFwMUpweEJiRExmLWFnQ2dTWTd6TXhKdnVYdi00dDRhU082bnhUREZWemR3X2Y0Ym5FSGZIeFE?oc=5</t>
         </is>
       </c>
-      <c r="V20" s="4" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr">
+      <c r="W20" s="3" t="inlineStr"/>
+      <c r="X20" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y20" s="4" t="inlineStr">
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>d8836955ecd1ed7c64c83def</t>
         </is>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AD20" s="3" t="inlineStr">
         <is>
           <t>020a5ea0bf202cedea432ffd</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr"/>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="inlineStr"/>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr"/>
-      <c r="AQ20" s="4" t="inlineStr"/>
-      <c r="AR20" s="4" t="inlineStr"/>
-      <c r="AS20" s="4" t="inlineStr"/>
-      <c r="AT20" s="4" t="inlineStr"/>
-      <c r="AU20" s="4" t="inlineStr"/>
-      <c r="AV20" s="4" t="inlineStr"/>
-      <c r="AW20" s="4" t="inlineStr">
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AM20" s="3" t="inlineStr"/>
+      <c r="AN20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr"/>
+      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AV20" s="3" t="inlineStr"/>
+      <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX20" s="4" t="inlineStr"/>
-      <c r="AY20" s="4" t="inlineStr"/>
-      <c r="AZ20" s="4" t="inlineStr"/>
-      <c r="BA20" s="4" t="inlineStr"/>
-      <c r="BB20" s="4" t="inlineStr">
+      <c r="AX20" s="3" t="inlineStr"/>
+      <c r="AY20" s="3" t="inlineStr"/>
+      <c r="AZ20" s="3" t="inlineStr"/>
+      <c r="BA20" s="3" t="inlineStr"/>
+      <c r="BB20" s="3" t="inlineStr">
         <is>
           <t>ADI</t>
         </is>
       </c>
-      <c r="BC20" s="4" t="inlineStr">
+      <c r="BC20" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="4" t="inlineStr"/>
-      <c r="BE20" s="4" t="inlineStr">
+      <c r="BD20" s="3" t="inlineStr"/>
+      <c r="BE20" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF20" s="4" t="inlineStr">
+      <c r="BF20" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG20" s="4" t="inlineStr">
+      <c r="BG20" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="4" t="inlineStr"/>
+      <c r="BH20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BJ20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr"/>
+      <c r="BL20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>SA analyst upgrades/downgrades: AAPL, IBM, UBER, HOG (IBM:NYSE)</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>'-0.428</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNY2pHXzZ0YWdQSFF1ODROWnRlN0I4YVdlTjBsWFVoVkVYZ0dsd0hkS25QbmxCakZpNHhPQWxMZ3Vxc3ZrSFQ1SnJYTXpoNmI2R0wyY2JfOTR0OGRqSDhLV3ZGVGRLZXc0TzVSVzlvTnRMbnE5OENEbXZ4YkxWajROSXhYekVPSl9DWjV4amZB?oc=5</t>
         </is>
       </c>
-      <c r="V21" s="4" t="inlineStr">
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y21" s="4" t="inlineStr">
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z21" s="4" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AD21" s="3" t="inlineStr">
         <is>
           <t>1305fc43f884bfc8862f9eaf</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr">
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="BC21" s="4" t="inlineStr">
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
+      <c r="BD21" s="3" t="inlineStr"/>
+      <c r="BE21" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="4" t="inlineStr">
+      <c r="BF21" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="4" t="inlineStr">
+      <c r="BG21" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="4" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr"/>
+      <c r="BL21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Tyson Foods: Headwinds Warrant Caution (Downgrade) (NYSE:TSN)</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>'-0.82</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPbWZsa3E5OUgySWE0bHZhWm40TzlUdXIwWmtpekJEcVJmZ1MwNTlXRFREdmdBaXZFTTFYTEl6MkJJdlZjSmVnakVlRlYtSHlJa3kyeXJUa2JsTjZYT28ySHIxelZ0QmpOZExOaFppRW45c0dfUjlrc2dvcEZzYmNDemJzR1hnUkhxbnVXTnJWOTFOdw?oc=5</t>
         </is>
       </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr">
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y22" s="4" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z22" s="4" t="inlineStr">
+      <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="inlineStr">
+      <c r="AA22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>108aa798b9a0975fcceb67db</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AD22" s="3" t="inlineStr">
         <is>
           <t>1969337db4f2364509d137ed</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr"/>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr"/>
+      <c r="AS22" s="3" t="inlineStr"/>
+      <c r="AT22" s="3" t="inlineStr"/>
+      <c r="AU22" s="3" t="inlineStr"/>
+      <c r="AV22" s="3" t="inlineStr"/>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX22" s="4" t="inlineStr"/>
-      <c r="AY22" s="4" t="inlineStr"/>
-      <c r="AZ22" s="4" t="inlineStr"/>
-      <c r="BA22" s="4" t="inlineStr"/>
-      <c r="BB22" s="4" t="inlineStr">
+      <c r="AX22" s="3" t="inlineStr"/>
+      <c r="AY22" s="3" t="inlineStr"/>
+      <c r="AZ22" s="3" t="inlineStr"/>
+      <c r="BA22" s="3" t="inlineStr"/>
+      <c r="BB22" s="3" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="BC22" s="4" t="inlineStr">
+      <c r="BC22" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD22" s="4" t="inlineStr"/>
-      <c r="BE22" s="4" t="inlineStr">
+      <c r="BD22" s="3" t="inlineStr"/>
+      <c r="BE22" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="4" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="4" t="inlineStr">
+      <c r="BG22" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BJ22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr"/>
+      <c r="BL22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH22"/>
+  <autoFilter ref="A1:BL22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4364,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4427,6 +4803,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4728,6 +5108,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4892,6 +5292,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5062,6 +5466,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5232,2349 +5640,1323 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Corteva, Inari Reach Confidential Settlement in Seed-Patent Case</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>FTC Settlement Limits Corteva Pesticide Loyalty Rebates</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.341</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>The Scoop -</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>c01631ea0f5c4f07b67037d7c8c17767</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>58e4a361c64031ce84799cb6</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>2dd32bc16b9d7b34926af28d</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.335</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdXVVRnh3WEx2TlBGVnFzcWR5bFNyUmcyakM4WVViQzduV19mc29yT2o0VDBHeXFOTV81SHM3T2YzeUxhYk05NGZGNXAyMHhSSmhfZVMzNzlLYUFxdU80aHY0NFNKb2ExMnN2RTRadVZDekJTZHV2Mzcya0xZamFVLUMxU3ZuVXhFQ3RKNGt3NC1ScFlZTFFpM3ZVODd0QmREUzF3QzB6Y2M1U2pY?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>1d4457fb5b4b603d601d65c9</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>8adb12c7bfd7adb7910757fe</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr"/>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>HCA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>HCA Healthcare, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>FTC Settlement Limits Corteva Pesticide Loyalty Rebates</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Can HCA Healthcare (HCA) Overcome Healthcare’s Margin Pressures?</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.341</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.531</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The Scoop -</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>58e4a361c64031ce84799cb6</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>2dd32bc16b9d7b34926af28d</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRTdEN243SHhreUdEVjZIZi1uSG8yaWp2ZklBQ0hxYk93ckhfeG9TOXVjVmJGZl9JTVBkZWk2NnVGczdWYTMzTWFxQlBYdHdFdV9NOGZXR2FpSkpaS0VtV0J0LUNkTUNCNWZjY01zRlRmdkZkWlotb0xsdjFRN0lvdWR6NUZGSWxTMm1Sem5tTF9xYkVkaTU4VWhUMHNJOXBG?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>cf3e9526fcc5f89a21b72559</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>e6bd5fc60dcaf770a8a58adc</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
+        <is>
+          <t>HCA</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>HCA</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>HCA Healthcare, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Can HCA Healthcare (HCA) Overcome Healthcare’s Margin Pressures?</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Corteva to End Pesticides Loyalty Program in Settlement With FTC</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.303</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>11716aa49bca4ff88bcc87ed06b74273</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>854069c078ef7dea44692cfc</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>96db35c9ac23729f442bd528</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.531</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRTdEN243SHhreUdEVjZIZi1uSG8yaWp2ZklBQ0hxYk93ckhfeG9TOXVjVmJGZl9JTVBkZWk2NnVGczdWYTMzTWFxQlBYdHdFdV9NOGZXR2FpSkpaS0VtV0J0LUNkTUNCNWZjY01zRlRmdkZkWlotb0xsdjFRN0lvdWR6NUZGSWxTMm1Sem5tTF9xYkVkaTU4VWhUMHNJOXBG?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>cf3e9526fcc5f89a21b72559</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>e6bd5fc60dcaf770a8a58adc</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
-        <is>
-          <t>HCA</t>
-        </is>
-      </c>
-      <c r="BC7" s="2" t="inlineStr">
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="2" t="inlineStr"/>
-      <c r="BE7" s="2" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="2" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="2" t="inlineStr">
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Corteva to End Pesticides Loyalty Program in Settlement With FTC</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Corteva reaches FTC antitrust settlement, agrees to $35M payment (CTVA:NYSE)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>67911ce819d3444591d6976b52d3134f</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>4b033dbf29afc311be67812a</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>add022a25ab732e3141ba5e8</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>'-0.303</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>854069c078ef7dea44692cfc</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>96db35c9ac23729f442bd528</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Corteva reaches FTC antitrust settlement, agrees to $35M payment (CTVA:NYSE)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>States, FTC secure settlement in suit against Corteva pesticide loyalty programs</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Iowa Capital Dispatch</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>2aacab99b13e4da492dd8f89a9d0ccb6</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>fa55d6f911a75d41e6f1ed9e</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>ef1fdace1b4d4ef928a14b4d</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>4b033dbf29afc311be67812a</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>add022a25ab732e3141ba5e8</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DRI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Darden Restaurants, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Paramount Woos Investors With Mega $44 Billion Debt Offer To Fund WBD Deal As Judge Weighs Settlement</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Darden Restaurants (DRI) Stock May Be 13% Undervalued After Q1 Earnings Miss</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>財報不如預期</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0.739</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.824</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOMGdyeENsY2VaOTFsZDdZNklRVUZWNDNQaXRKd0p1dENQZlg4dnpWdnJuYmdZd0JLaHhaT29oX1MyMDBpdVRiUGhFRHgzcTR2alVPeXNMZXZaaC1VQnVoVTlzWV90d05salFZd1ZVVHNLY2NPTkxxYy1ZQzVBLXBBSGFVMjlTS2RhRHNQTHZvU05tbHBHeGllUWJlNA?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>7e5c915e760701c5b0c0bd28</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>7e7c450d2aff2615a726b546</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaXdua1JwcHFmRjRLZzV5NTBBcFhtQ280UERYQ3Z2Ul8zNUw3cVlqTWhhU2JOVHNJbS1pSFBwRDFMdklOSUJTSldCUTZDckZiQ2dnSEVzdnRmMVVmcVZLR0xfQXVLRUxLdXlUcl9PZHRpYTZtaDhRMExmRENzdHNLai1keDJaektNR01VTHZqT3REcVQzQkt5UllINVp3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>EARNINGS_MISS</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>b601ce027011be46f62ff559</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>260bef3068ad46f360e48c7b</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
+        <is>
+          <t>DRI</t>
+        </is>
+      </c>
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG10" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>States, FTC secure settlement in suit against Corteva pesticide loyalty programs</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>PNR DEADLINE NOTICE: Faruqi &amp; Faruqi, LLP Reminds Pentair (PNR) Investors of Securities Class Action Lawsuit Deadline on October 2, 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>'-0.068</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>f1d55caddc654688b58c6fb579b28c84</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>e219e320bea4f382169bc711</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>3b46f49745e60c6b38e6f5c0</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Iowa Capital Dispatch</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>fa55d6f911a75d41e6f1ed9e</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>ef1fdace1b4d4ef928a14b4d</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr"/>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Corteva and Inari Reach Settlement Agreement</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>0.457</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQOUNldEx2U2VwSVhZeUFNdjIzdWFLN09hOWkwRFBTUDN0MzJRWURYMzQ4d2pUTm1HdFl2OXFyQWdVMS1vU0xjSVBzV0ZCZExVckxTVk9DS3p4UXRZMHhFYmR3MFFHN2dra1BoaXpYX2ZUOG1FOVVQWlhKMTZPblg2aHRMemhnaWpkUno1bmItTGI0RTFZYWgwdlpXNGFQUEtteXc?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>eba33791b81f597b4205d71a</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>018432c867f6de5ef5bd678e</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>CFTC Approves Coinbase Clearing as First USDC-Native Clearinghouse</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>0.441</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNSWp4NmVhejh4bG5ZYXRVOFVaZ1g2VXVGYWZXUlZETTdGdVJ2NDdPRlMybkhVSEZrbk1tTHFMTzFVdEs2cE1qMzFZdml4cDNBTXFvaXJTTm5wSVpSd3ZVZHFkVWdGN3lTSkpZN0x4NzQyc05UX0h0Qmk1UXdabVpVeEtHMVlSTF9VcGNyZl9mdmRnWjJBLWJ3WFowNk45R05VRjBnZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="inlineStr">
-        <is>
-          <t>fb8abff601832e31f53924b5</t>
-        </is>
-      </c>
-      <c r="AD13" s="3" t="inlineStr">
-        <is>
-          <t>2e351af99116e7943321cb38</t>
-        </is>
-      </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC13" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="3" t="inlineStr"/>
-      <c r="BG13" s="3" t="inlineStr">
+      <c r="BF11" s="4" t="inlineStr"/>
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase Receives CFTC Approval for Coinbase Clearing LLC</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.327</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNYzRxS3dnUk9NS1JSNzJEOW9kRDVJdUFWTTlmWEdtYUlTeGdUU3ZrTHU5R0ZXLXZkRDVqbGdLb1lWZUJvb1BqcDRqelNCeElMSnk0eVpWcmM3UXJSZHhRYWxlRE1Gb1E1cFZFOWZBR01tZGFEZUlOSk56MW1iaDVXMkVfNUgzeHZQY29kbXdsSng?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>883f49f228b9610ccb17dbef</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>7e19b35937027c989c531e77</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase Brings Derivatives Clearing In-House After CFTC Registration</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZTYtVnBkNGg5RTBvR0k0dVBwOVVBaFpwUFBCZGppMmh3dDU3b0didkdpRXZYWGZuaDVmNElhUnAyQUR0bnNMY2stYk5zd2ROV1FNQ2paYUVEWUxOT2w4WlNRdUJyVWxlemtTV0NuZkhtVkFCQkI1WF9FbmxqV1lHSnRUQUhPZnJZamYtZmNVZ3N4d1lzOE5YY3FaQkhCZHF1c1JjdTFHUEpSUmM?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>2a6cdf6613b7924e2889db28</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>8ef66e4facf6b2e8d09fa3b9</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants (DRI) Stock May Be 13% Undervalued After Q1 Earnings Miss</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>'-0.824</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaXdua1JwcHFmRjRLZzV5NTBBcFhtQ280UERYQ3Z2Ul8zNUw3cVlqTWhhU2JOVHNJbS1pSFBwRDFMdklOSUJTSldCUTZDckZiQ2dnSEVzdnRmMVVmcVZLR0xfQXVLRUxLdXlUcl9PZHRpYTZtaDhRMExmRENzdHNLai1keDJaektNR01VTHZqT3REcVQzQkt5UllINVp3UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>b601ce027011be46f62ff559</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>260bef3068ad46f360e48c7b</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr"/>
-      <c r="AF16" s="2" t="inlineStr"/>
-      <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr"/>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr"/>
-      <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr"/>
-      <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
-      <c r="AP16" s="2" t="inlineStr"/>
-      <c r="AQ16" s="2" t="inlineStr"/>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="inlineStr"/>
-      <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="2" t="inlineStr"/>
-      <c r="AY16" s="2" t="inlineStr"/>
-      <c r="AZ16" s="2" t="inlineStr"/>
-      <c r="BA16" s="2" t="inlineStr"/>
-      <c r="BB16" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="BC16" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="2" t="inlineStr"/>
-      <c r="BE16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>PNR DEADLINE NOTICE: Faruqi &amp; Faruqi, LLP Reminds Pentair (PNR) Investors of Securities Class Action Lawsuit Deadline on October 2, 2026</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
-        <is>
-          <t>e219e320bea4f382169bc711</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>3b46f49745e60c6b38e6f5c0</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC17" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Used the CVS app? You may be owed part of $20.5M digital privacy settlement in NC</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>'-0.067</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE80OThzamZkSTdaLVRzeExaa0lzb2t3bEhVR05ST3RDYldGREQ3ZjRoS1ZSRWRHQXFFd25VY3dZbWZLMTY3NTRiVHd6eXdLZ3JJWDByN2ZMZ3JZcnd3bk8yajduZHRkUjFxaEdvb2QtNGdHRThpSVQ1Tg?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Charlotte Observer</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="inlineStr">
-        <is>
-          <t>a5d0531db2cabc233a69b07d</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>37b4cfd575badb09af23c678</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="BC18" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH18" s="3" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH18"/>
+  <autoFilter ref="A1:BL11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7585,7 +6967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7648,6 +7030,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7951,9 +7337,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7964,7 +7370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8027,6 +7433,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8330,9 +7740,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8343,7 +7773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8393,477 +7823,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-28.xlsx
+++ b/news_daily/2026-09-28.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>EXPORT_RESTRICTION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>7b397c423a5443588b1c5f0530c05ef0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>d2cc2b0d3f22ac6ae8017dd7</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1015,10 +1027,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1054,28 +1078,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1115,7 +1143,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1124,7 +1152,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>ce757d0c525341a7935389fc44cfee15</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>9cf3d8f581d280a2ce1327fe</t>
@@ -1145,7 +1177,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1189,378 +1225,410 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Pfizer, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Pfizer, Moderna lose bids to escape Bayer US mRNA patent lawsuit</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>專利訴訟</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.902</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdUNZWjdnUDRDZ1B1M0M2Rjg2bU5GWFZhdlFQZjB1MlBDZkd4Z2QxV1NRNy04d3RHcjFXdFJZdlBrNURDSEdudmxjNHZ2OGpjOXVLRHFEYmMtOVNfVUNsbjc0RFNXSW5XcWtPTm02Y0hMR2szQW5QUDFwcFNNRjZNMkZqbXBHVVJCdjJLNG95ZC1XRlU5dHVsbXM0SFcwelBINXI4MVBsTUpPaU1DbjRMR3lBbzJ5M2M?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>PATENT_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>patent lawsuit</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>6e5f81529c774f88bcf0c4fe2feb5cc4</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>8c126ffc7a3abe9b63f12473</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>80449a1b7ea075a3a7440d89</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.902</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdUNZWjdnUDRDZ1B1M0M2Rjg2bU5GWFZhdlFQZjB1MlBDZkd4Z2QxV1NRNy04d3RHcjFXdFJZdlBrNURDSEdudmxjNHZ2OGpjOXVLRHFEYmMtOVNfVUNsbjc0RFNXSW5XcWtPTm02Y0hMR2szQW5QUDFwcFNNRjZNMkZqbXBHVVJCdjJLNG95ZC1XRlU5dHVsbXM0SFcwelBINXI4MVBsTUpPaU1DbjRMR3lBbzJ5M2M?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>PATENT_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>patent lawsuit</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>8c126ffc7a3abe9b63f12473</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>80449a1b7ea075a3a7440d89</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>PFE</t>
         </is>
       </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Corteva, Inari Reach Confidential Settlement in Seed-Patent Case</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>'-0.335</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQdXVVRnh3WEx2TlBGVnFzcWR5bFNyUmcyakM4WVViQzduV19mc29yT2o0VDBHeXFOTV81SHM3T2YzeUxhYk05NGZGNXAyMHhSSmhfZVMzNzlLYUFxdU80aHY0NFNKb2ExMnN2RTRadVZDekJTZHV2Mzcya0xZamFVLUMxU3ZuVXhFQ3RKNGt3NC1ScFlZTFFpM3ZVODd0QmREUzF3QzB6Y2M1U2pY?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="3" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>ad24e6be1d7c42b8bb6df1c5b9d33101</t>
         </is>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>1d4457fb5b4b603d601d65c9</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
+      <c r="AD5" s="2" t="inlineStr">
         <is>
           <t>8adb12c7bfd7adb7910757fe</t>
         </is>
       </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr">
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr">
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL5" s="3" t="inlineStr">
+      <c r="BL5" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -1794,28 +1862,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1855,7 +1927,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1864,7 +1936,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>97d2eb1d513b4a2b8a7b76e9757dc688</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>cf3e9526fcc5f89a21b72559</t>
@@ -1885,7 +1961,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1929,10 +2009,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2323,190 +2415,190 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Warner Bros. Discovery</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Paramount Woos Investors With Mega $44 Billion Debt Offer To Fund WBD Deal As Judge Weighs Settlement</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0.739</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOMGdyeENsY2VaOTFsZDdZNklRVUZWNDNQaXRKd0p1dENQZlg4dnpWdnJuYmdZd0JLaHhaT29oX1MyMDBpdVRiUGhFRHgzcTR2alVPeXNMZXZaaC1VQnVoVTlzWV90d05salFZd1ZVVHNLY2NPTkxxYy1ZQzVBLXBBSGFVMjlTS2RhRHNQTHZvU05tbHBHeGllUWJlNA?oc=5</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>cfe9a633a44a4d83a1a210ee983786cd</t>
         </is>
       </c>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>7e5c915e760701c5b0c0bd28</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="inlineStr">
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>7e7c450d2aff2615a726b546</t>
         </is>
       </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr">
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr">
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL10" s="3" t="inlineStr">
+      <c r="BL10" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -2707,768 +2799,768 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corteva, Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Corteva and Inari Reach Settlement Agreement</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0.457</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQOUNldEx2U2VwSVhZeUFNdjIzdWFLN09hOWkwRFBTUDN0MzJRWURYMzQ4d2pUTm1HdFl2OXFyQWdVMS1vU0xjSVBzV0ZCZExVckxTVk9DS3p4UXRZMHhFYmR3MFFHN2dra1BoaXpYX2ZUOG1FOVVQWlhKMTZPblg2aHRMemhnaWpkUno1bmItTGI0RTFZYWgwdlpXNGFQUEtteXc?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="3" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>PR Newswire</t>
         </is>
       </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>8fee310a77674df0a73f9e3870b6236f</t>
         </is>
       </c>
-      <c r="AC12" s="3" t="inlineStr">
+      <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>eba33791b81f597b4205d71a</t>
         </is>
       </c>
-      <c r="AD12" s="3" t="inlineStr">
+      <c r="AD12" s="2" t="inlineStr">
         <is>
           <t>018432c867f6de5ef5bd678e</t>
         </is>
       </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr">
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>CTVA</t>
         </is>
       </c>
-      <c r="BC12" s="3" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr">
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr">
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="3" t="inlineStr">
+      <c r="BL12" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>CFTC Approves Coinbase Clearing as First USDC-Native Clearinghouse</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0.441</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNSWp4NmVhejh4bG5ZYXRVOFVaZ1g2VXVGYWZXUlZETTdGdVJ2NDdPRlMybkhVSEZrbk1tTHFMTzFVdEs2cE1qMzFZdml4cDNBTXFvaXJTTm5wSVpSd3ZVZHFkVWdGN3lTSkpZN0x4NzQyc05UX0h0Qmk1UXdabVpVeEtHMVlSTF9VcGNyZl9mdmRnWjJBLWJ3WFowNk45R05VRjBnZw?oc=5</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>CFTC；FTC</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>f0d4bf2d2b994dc1b1ba1a80292aa45b</t>
         </is>
       </c>
-      <c r="AC13" s="3" t="inlineStr">
+      <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>fb8abff601832e31f53924b5</t>
         </is>
       </c>
-      <c r="AD13" s="3" t="inlineStr">
+      <c r="AD13" s="2" t="inlineStr">
         <is>
           <t>2e351af99116e7943321cb38</t>
         </is>
       </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr">
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC13" s="3" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="3" t="inlineStr"/>
-      <c r="BG13" s="3" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr">
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr">
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL13" s="3" t="inlineStr">
+      <c r="BL13" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Coinbase Receives CFTC Approval for Coinbase Clearing LLC</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0.327</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNYzRxS3dnUk9NS1JSNzJEOW9kRDVJdUFWTTlmWEdtYUlTeGdUU3ZrTHU5R0ZXLXZkRDVqbGdLb1lWZUJvb1BqcDRqelNCeElMSnk0eVpWcmM3UXJSZHhRYWxlRE1Gb1E1cFZFOWZBR01tZGFEZUlOSk56MW1iaDVXMkVfNUgzeHZQY29kbXdsSng?oc=5</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>CFTC；FTC</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>e15cfa024e314823a07a6d3c033d3a41</t>
         </is>
       </c>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>883f49f228b9610ccb17dbef</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="inlineStr">
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>7e19b35937027c989c531e77</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr"/>
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr">
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr">
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL14" s="3" t="inlineStr">
+      <c r="BL14" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Coinbase Brings Derivatives Clearing In-House After CFTC Registration</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0.025</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZTYtVnBkNGg5RTBvR0k0dVBwOVVBaFpwUFBCZGppMmh3dDU3b0didkdpRXZYWGZuaDVmNElhUnAyQUR0bnNMY2stYk5zd2ROV1FNQ2paYUVEWUxOT2w4WlNRdUJyVWxlemtTV0NuZkhtVkFCQkI1WF9FbmxqV1lHSnRUQUhPZnJZamYtZmNVZ3N4d1lzOE5YY3FaQkhCZHF1c1JjdTFHUEpSUmM?oc=5</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>CFTC；FTC</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>f0711541479e401c9c83cd2d1b80d367</t>
         </is>
       </c>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>2a6cdf6613b7924e2889db28</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="inlineStr">
+      <c r="AD15" s="2" t="inlineStr">
         <is>
           <t>8ef66e4facf6b2e8d09fa3b9</t>
         </is>
       </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr">
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr">
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr">
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL15" s="3" t="inlineStr">
+      <c r="BL15" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -3508,28 +3600,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3569,7 +3665,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3578,7 +3674,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>e104793c55e346d4830da13948e54699</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>b601ce027011be46f62ff559</t>
@@ -3599,7 +3699,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3643,10 +3747,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3835,898 +3951,898 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>CVS Health Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Used the CVS app? You may be owed part of $20.5M digital privacy settlement in NC</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>無關新聞事件</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>排除、不納入風險事件</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>'-0.067</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE80OThzamZkSTdaLVRzeExaa0lzb2t3bEhVR05ST3RDYldGREQ3ZjRoS1ZSRWRHQXFFd25VY3dZbWZLMTY3NTRiVHd6eXdLZ3JJWDByN2ZMZ3JZcnd3bk8yajduZHRkUjFxaEdvb2QtNGdHRThpSVQ1Tg?oc=5</t>
         </is>
       </c>
-      <c r="V18" s="3" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Charlotte Observer</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>NOT_RELEVANT</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>fb3cbda1c08d4432a26eb521753d031c</t>
         </is>
       </c>
-      <c r="AC18" s="3" t="inlineStr">
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>a5d0531db2cabc233a69b07d</t>
         </is>
       </c>
-      <c r="AD18" s="3" t="inlineStr">
+      <c r="AD18" s="2" t="inlineStr">
         <is>
           <t>37b4cfd575badb09af23c678</t>
         </is>
       </c>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
-      <c r="AM18" s="3" t="inlineStr"/>
-      <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr">
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
+      <c r="AL18" s="2" t="inlineStr"/>
+      <c r="AM18" s="2" t="inlineStr"/>
+      <c r="AN18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
-      <c r="AV18" s="3" t="inlineStr"/>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AP18" s="2" t="inlineStr"/>
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX18" s="3" t="inlineStr"/>
-      <c r="AY18" s="3" t="inlineStr"/>
-      <c r="AZ18" s="3" t="inlineStr"/>
-      <c r="BA18" s="3" t="inlineStr"/>
-      <c r="BB18" s="3" t="inlineStr">
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr"/>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
         <is>
           <t>CVS</t>
         </is>
       </c>
-      <c r="BC18" s="3" t="inlineStr">
+      <c r="BC18" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD18" s="3" t="inlineStr"/>
-      <c r="BE18" s="3" t="inlineStr">
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF18" s="3" t="inlineStr">
+      <c r="BF18" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG18" s="3" t="inlineStr">
+      <c r="BG18" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr">
+      <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
         <is>
           <t>Action|Event_Code|Level|事件中文</t>
         </is>
       </c>
-      <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr">
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL18" s="3" t="inlineStr">
+      <c r="BL18" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>SA analyst upgrades/downgrades: AAPL, IBM, UBER, HOG (IBM:NYSE)</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>'-0.428</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNY2pHXzZ0YWdQSFF1ODROWnRlN0I4YVdlTjBsWFVoVkVYZ0dsd0hkS25QbmxCakZpNHhPQWxMZ3Vxc3ZrSFQ1SnJYTXpoNmI2R0wyY2JfOTR0OGRqSDhLV3ZGVGRLZXc0TzVSVzlvTnRMbnE5OENEbXZ4YkxWajROSXhYekVPSl9DWjV4amZB?oc=5</t>
         </is>
       </c>
-      <c r="V19" s="3" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
         </is>
       </c>
-      <c r="AD19" s="3" t="inlineStr">
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>66e36ff245e18d26ca3537a8</t>
         </is>
       </c>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
-      <c r="AM19" s="3" t="inlineStr"/>
-      <c r="AN19" s="3" t="inlineStr"/>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="3" t="inlineStr">
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX19" s="3" t="inlineStr"/>
-      <c r="AY19" s="3" t="inlineStr"/>
-      <c r="AZ19" s="3" t="inlineStr"/>
-      <c r="BA19" s="3" t="inlineStr"/>
-      <c r="BB19" s="3" t="inlineStr">
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC19" s="3" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="3" t="inlineStr"/>
-      <c r="BE19" s="3" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF19" s="3" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG19" s="3" t="inlineStr">
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH19" s="3" t="inlineStr"/>
-      <c r="BI19" s="3" t="inlineStr"/>
-      <c r="BJ19" s="3" t="inlineStr"/>
-      <c r="BK19" s="3" t="inlineStr"/>
-      <c r="BL19" s="3" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>ADI</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Analog Devices, Inc.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>ADI Global Distribution Shares Fall After Evercore ISI Initiates With In Line Rating</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>'-0.95</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOR2hFZHhDaWRUSVBNeXRURGpaRUNDY1BFRC1kQkFhbGxSb2NEQWhZbENCcjZPOUYzdXJqanVLQXZOTnNmT25NTG1PX3lKYVNSc3dUbUllX3FybFdqa3FlR05HSnhUR1N0UEJLVzFwMUpweEJiRExmLWFnQ2dTWTd6TXhKdnVYdi00dDRhU082bnhUREZWemR3X2Y0Ym5FSGZIeFE?oc=5</t>
         </is>
       </c>
-      <c r="V20" s="3" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>d8836955ecd1ed7c64c83def</t>
         </is>
       </c>
-      <c r="AD20" s="3" t="inlineStr">
+      <c r="AD20" s="2" t="inlineStr">
         <is>
           <t>020a5ea0bf202cedea432ffd</t>
         </is>
       </c>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
-      <c r="AM20" s="3" t="inlineStr"/>
-      <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
-      <c r="AV20" s="3" t="inlineStr"/>
-      <c r="AW20" s="3" t="inlineStr">
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr"/>
+      <c r="AL20" s="2" t="inlineStr"/>
+      <c r="AM20" s="2" t="inlineStr"/>
+      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AP20" s="2" t="inlineStr"/>
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr"/>
+      <c r="AS20" s="2" t="inlineStr"/>
+      <c r="AT20" s="2" t="inlineStr"/>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX20" s="3" t="inlineStr"/>
-      <c r="AY20" s="3" t="inlineStr"/>
-      <c r="AZ20" s="3" t="inlineStr"/>
-      <c r="BA20" s="3" t="inlineStr"/>
-      <c r="BB20" s="3" t="inlineStr">
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr"/>
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr">
         <is>
           <t>ADI</t>
         </is>
       </c>
-      <c r="BC20" s="3" t="inlineStr">
+      <c r="BC20" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="3" t="inlineStr"/>
-      <c r="BE20" s="3" t="inlineStr">
+      <c r="BD20" s="2" t="inlineStr"/>
+      <c r="BE20" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF20" s="3" t="inlineStr">
+      <c r="BF20" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG20" s="3" t="inlineStr">
+      <c r="BG20" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="3" t="inlineStr"/>
-      <c r="BI20" s="3" t="inlineStr"/>
-      <c r="BJ20" s="3" t="inlineStr"/>
-      <c r="BK20" s="3" t="inlineStr"/>
-      <c r="BL20" s="3" t="inlineStr"/>
+      <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SA analyst upgrades/downgrades: AAPL, IBM, UBER, HOG (IBM:NYSE)</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>'-0.428</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNY2pHXzZ0YWdQSFF1ODROWnRlN0I4YVdlTjBsWFVoVkVYZ0dsd0hkS25QbmxCakZpNHhPQWxMZ3Vxc3ZrSFQ1SnJYTXpoNmI2R0wyY2JfOTR0OGRqSDhLV3ZGVGRLZXc0TzVSVzlvTnRMbnE5OENEbXZ4YkxWajROSXhYekVPSl9DWjV4amZB?oc=5</t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
         </is>
       </c>
-      <c r="AD21" s="3" t="inlineStr">
+      <c r="AD21" s="2" t="inlineStr">
         <is>
           <t>1305fc43f884bfc8862f9eaf</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr"/>
-      <c r="AF21" s="3" t="inlineStr"/>
-      <c r="AG21" s="3" t="inlineStr"/>
-      <c r="AH21" s="3" t="inlineStr"/>
-      <c r="AI21" s="3" t="inlineStr"/>
-      <c r="AJ21" s="3" t="inlineStr"/>
-      <c r="AK21" s="3" t="inlineStr"/>
-      <c r="AL21" s="3" t="inlineStr"/>
-      <c r="AM21" s="3" t="inlineStr"/>
-      <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
-      <c r="AP21" s="3" t="inlineStr"/>
-      <c r="AQ21" s="3" t="inlineStr"/>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr"/>
-      <c r="AV21" s="3" t="inlineStr"/>
-      <c r="AW21" s="3" t="inlineStr">
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr"/>
+      <c r="AL21" s="2" t="inlineStr"/>
+      <c r="AM21" s="2" t="inlineStr"/>
+      <c r="AN21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AP21" s="2" t="inlineStr"/>
+      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AR21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr"/>
+      <c r="AT21" s="2" t="inlineStr"/>
+      <c r="AU21" s="2" t="inlineStr"/>
+      <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX21" s="3" t="inlineStr"/>
-      <c r="AY21" s="3" t="inlineStr"/>
-      <c r="AZ21" s="3" t="inlineStr"/>
-      <c r="BA21" s="3" t="inlineStr"/>
-      <c r="BB21" s="3" t="inlineStr">
+      <c r="AX21" s="2" t="inlineStr"/>
+      <c r="AY21" s="2" t="inlineStr"/>
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="BC21" s="3" t="inlineStr">
+      <c r="BC21" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="3" t="inlineStr"/>
-      <c r="BE21" s="3" t="inlineStr">
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="3" t="inlineStr">
+      <c r="BF21" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="3" t="inlineStr">
+      <c r="BG21" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="3" t="inlineStr"/>
-      <c r="BI21" s="3" t="inlineStr"/>
-      <c r="BJ21" s="3" t="inlineStr"/>
-      <c r="BK21" s="3" t="inlineStr"/>
-      <c r="BL21" s="3" t="inlineStr"/>
+      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Tyson Foods: Headwinds Warrant Caution (Downgrade) (NYSE:TSN)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>分析師降評</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>'-0.82</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPbWZsa3E5OUgySWE0bHZhWm40TzlUdXIwWmtpekJEcVJmZ1MwNTlXRFREdmdBaXZFTTFYTEl6MkJJdlZjSmVnakVlRlYtSHlJa3kyeXJUa2JsTjZYT28ySHIxelZ0QmpOZExOaFppRW45c0dfUjlrc2dvcEZzYmNDemJzR1hnUkhxbnVXTnJWOTFOdw?oc=5</t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Seeking Alpha</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>ANALYST_DOWNGRADE</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>downgrade</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>108aa798b9a0975fcceb67db</t>
         </is>
       </c>
-      <c r="AD22" s="3" t="inlineStr">
+      <c r="AD22" s="2" t="inlineStr">
         <is>
           <t>1969337db4f2364509d137ed</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
-      <c r="AM22" s="3" t="inlineStr"/>
-      <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
-      <c r="AV22" s="3" t="inlineStr"/>
-      <c r="AW22" s="3" t="inlineStr">
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr"/>
+      <c r="AS22" s="2" t="inlineStr"/>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX22" s="3" t="inlineStr"/>
-      <c r="AY22" s="3" t="inlineStr"/>
-      <c r="AZ22" s="3" t="inlineStr"/>
-      <c r="BA22" s="3" t="inlineStr"/>
-      <c r="BB22" s="3" t="inlineStr">
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr"/>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="BC22" s="3" t="inlineStr">
+      <c r="BC22" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD22" s="3" t="inlineStr"/>
-      <c r="BE22" s="3" t="inlineStr">
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="3" t="inlineStr">
+      <c r="BF22" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="3" t="inlineStr">
+      <c r="BG22" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
-      <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BH22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL22"/>
@@ -4740,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL11"/>
+  <dimension ref="A1:BL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5132,518 +5248,586 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28T17:32:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>How a U.S. diesel export ban would play out, according to Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pfizer, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Pfizer, Moderna lose bids to escape Bayer US mRNA patent lawsuit</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>出口管制</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>專利訴訟</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.902</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdUNZWjdnUDRDZ1B1M0M2Rjg2bU5GWFZhdlFQZjB1MlBDZkd4Z2QxV1NRNy04d3RHcjFXdFJZdlBrNURDSEdudmxjNHZ2OGpjOXVLRHFEYmMtOVNfVUNsbjc0RFNXSW5XcWtPTm02Y0hMR2szQW5QUDFwcFNNRjZNMkZqbXBHVVJCdjJLNG95ZC1XRlU5dHVsbXM0SFcwelBINXI4MVBsTUpPaU1DbjRMR3lBbzJ5M2M?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>PATENT_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>patent lawsuit</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>6e5f81529c774f88bcf0c4fe2feb5cc4</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>8c126ffc7a3abe9b63f12473</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>80449a1b7ea075a3a7440d89</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.124</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQM1U4MjNFX3hFWXE1bGVfb1hSTDFEZ0FfOURDdERGV05iRHpScXRLb254VEV4QmxtU3JPcDEyM2V3LVZlS2s3TXFNbUVpekZKMTNGTWZNNTRZakZidFY3TFZrUE80UW5MekZITEo1elRnNXRHWENDM3V3UU1SRGZaN3c3VWUxZjJieVh4UWtqbUlqQnNYQThtWU5rczBhNzFLS1h5ZTlBOEN0MDdIdEV5OEp3?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>MarketWatch</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>EXPORT_RESTRICTION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>export ban</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>d2cc2b0d3f22ac6ae8017dd7</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>d431b18069310d29cc900ab8</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr"/>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr"/>
-      <c r="BG2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>EXC</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Exelon Corporation</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28T16:28:44+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Exelon stock faces lower targets after Q2 earnings miss</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FTC Settlement Limits Corteva Pesticide Loyalty Rebates</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>'-0.341</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>The Scoop -</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>c01631ea0f5c4f07b67037d7c8c17767</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>58e4a361c64031ce84799cb6</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>2dd32bc16b9d7b34926af28d</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
+      <c r="AL3" s="4" t="inlineStr"/>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.831</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQM1lqYjlwUVpXUkNzV0VpNlh5YjNlb3lpNnczMGxZVzZfMEJ4V1hseWFzaDVVRmluMlVnMDhBRV9yRlo1UjVrTVFCNGh5WTdzeTJHMnlSOWp0d2EzRUVTdDN2Z3lJd1JUVVctZ0hBbjN1ajJOZ1JXUzJSUk1MWjJub0xkSzlfVFNlbFlFY2FybkhTRm5PR3FYMHBSaFRLNW9uRGZtaGVPVXg0dkhpV1pqODNCVUs0U1p1UUE?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>ad-hoc-news.de</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>9cf3d8f581d280a2ce1327fe</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>30b53c78b9a25a4a3af002ef</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>EXC</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
+      <c r="AP3" s="4" t="inlineStr"/>
+      <c r="AQ3" s="4" t="inlineStr"/>
+      <c r="AR3" s="4" t="inlineStr"/>
+      <c r="AS3" s="4" t="inlineStr"/>
+      <c r="AT3" s="4" t="inlineStr"/>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr"/>
+      <c r="AY3" s="4" t="inlineStr"/>
+      <c r="AZ3" s="4" t="inlineStr"/>
+      <c r="BA3" s="4" t="inlineStr"/>
+      <c r="BB3" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC3" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="2" t="inlineStr"/>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr">
+      <c r="BD3" s="4" t="inlineStr"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG3" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BI3" s="4" t="inlineStr"/>
+      <c r="BJ3" s="4" t="inlineStr"/>
+      <c r="BK3" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Pfizer, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Pfizer, Moderna lose bids to escape Bayer US mRNA patent lawsuit</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>專利訴訟</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Corteva to End Pesticides Loyalty Program in Settlement With FTC</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>'-0.303</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>11716aa49bca4ff88bcc87ed06b74273</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>854069c078ef7dea44692cfc</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>96db35c9ac23729f442bd528</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr"/>
+      <c r="AF4" s="4" t="inlineStr"/>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.902</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdUNZWjdnUDRDZ1B1M0M2Rjg2bU5GWFZhdlFQZjB1MlBDZkd4Z2QxV1NRNy04d3RHcjFXdFJZdlBrNURDSEdudmxjNHZ2OGpjOXVLRHFEYmMtOVNfVUNsbjc0RFNXSW5XcWtPTm02Y0hMR2szQW5QUDFwcFNNRjZNMkZqbXBHVVJCdjJLNG95ZC1XRlU5dHVsbXM0SFcwelBINXI4MVBsTUpPaU1DbjRMR3lBbzJ5M2M?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>PATENT_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>patent lawsuit</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>8c126ffc7a3abe9b63f12473</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>80449a1b7ea075a3a7440d89</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr">
+      <c r="AP4" s="4" t="inlineStr"/>
+      <c r="AQ4" s="4" t="inlineStr"/>
+      <c r="AR4" s="4" t="inlineStr"/>
+      <c r="AS4" s="4" t="inlineStr"/>
+      <c r="AT4" s="4" t="inlineStr"/>
+      <c r="AU4" s="4" t="inlineStr"/>
+      <c r="AV4" s="4" t="inlineStr"/>
+      <c r="AW4" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
+      <c r="AX4" s="4" t="inlineStr"/>
+      <c r="AY4" s="4" t="inlineStr"/>
+      <c r="AZ4" s="4" t="inlineStr"/>
+      <c r="BA4" s="4" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="2" t="inlineStr"/>
-      <c r="BE4" s="2" t="inlineStr">
+      <c r="BD4" s="4" t="inlineStr"/>
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="2" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="2" t="inlineStr">
+      <c r="BG4" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5673,7 +5857,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>FTC Settlement Limits Corteva Pesticide Loyalty Rebates</t>
+          <t>Corteva reaches FTC antitrust settlement, agrees to $35M payment (CTVA:NYSE)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -5714,7 +5898,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>'-0.341</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
@@ -5728,12 +5912,12 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQTXNBZklSdFF6VXVZS3hSZDBQME1NUWU4WHFzUXpHZmQ4RzBRZERQVUhZMjZsSThTYzNqQlluT0t2a3VpS044aDVqcG5GWHFnTmZhaVdpWFNyVm5TZmVheC1aYVlsdlB1V3BTX0NyMl9FczBqbjNEa0pUNWlXcHNJT0NpMkZ5bEJxNmw0U3Q3bER3LWw2aTBIR1VobGltcVlmd1BjZFR1c2dyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>The Scoop -</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr"/>
@@ -5755,17 +5939,17 @@
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr">
         <is>
-          <t>c01631ea0f5c4f07b67037d7c8c17767</t>
+          <t>67911ce819d3444591d6976b52d3134f</t>
         </is>
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>58e4a361c64031ce84799cb6</t>
+          <t>4b033dbf29afc311be67812a</t>
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>2dd32bc16b9d7b34926af28d</t>
+          <t>add022a25ab732e3141ba5e8</t>
         </is>
       </c>
       <c r="AE5" s="4" t="inlineStr"/>
@@ -5840,178 +6024,198 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>HCA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>HCA Healthcare, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-28T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Can HCA Healthcare (HCA) Overcome Healthcare’s Margin Pressures?</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>States, FTC secure settlement in suit against Corteva pesticide loyalty programs</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Iowa Capital Dispatch</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>2aacab99b13e4da492dd8f89a9d0ccb6</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>fa55d6f911a75d41e6f1ed9e</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>ef1fdace1b4d4ef928a14b4d</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.531</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRTdEN243SHhreUdEVjZIZi1uSG8yaWp2ZklBQ0hxYk93ckhfeG9TOXVjVmJGZl9JTVBkZWk2NnVGczdWYTMzTWFxQlBYdHdFdV9NOGZXR2FpSkpaS0VtV0J0LUNkTUNCNWZjY01zRlRmdkZkWlotb0xsdjFRN0lvdWR6NUZGSWxTMm1Sem5tTF9xYkVkaTU4VWhUMHNJOXBG?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>cf3e9526fcc5f89a21b72559</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>e6bd5fc60dcaf770a8a58adc</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>HCA</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>CTVA</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="inlineStr">
+      <c r="BF6" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="2" t="inlineStr">
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6026,12 +6230,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -6041,7 +6245,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Corteva to End Pesticides Loyalty Program in Settlement With FTC</t>
+          <t>PNR DEADLINE NOTICE: Faruqi &amp; Faruqi, LLP Reminds Pentair (PNR) Investors of Securities Class Action Lawsuit Deadline on October 2, 2026</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -6052,7 +6256,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -6082,7 +6286,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>'-0.303</t>
+          <t>'-0.068</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -6096,12 +6300,12 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQT3ZtNDV2ZWplSmlrQkRFZ05zSjNFc2M4OFRfa082TGo1cGNaWllGTTMxNjlUQm13NnlZeExZaGtzVC1LMUFBblZDRXlxdUpUYlc3STBUb3dqSTJiWWNKTHRjLV8tbXpjcUZnblYwdEZUUUNQX3BOWUFhc0ZZM1hQTlMxY1l3RHdJZk1QUDE2cF9SOTN4S05mQ1FGT0NfMVFxaGNZaW5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
@@ -6112,28 +6316,28 @@
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr"/>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>11716aa49bca4ff88bcc87ed06b74273</t>
+          <t>f1d55caddc654688b58c6fb579b28c84</t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>854069c078ef7dea44692cfc</t>
+          <t>e219e320bea4f382169bc711</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>96db35c9ac23729f442bd528</t>
+          <t>3b46f49745e60c6b38e6f5c0</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -6158,18 +6362,14 @@
       <c r="AT7" s="4" t="inlineStr"/>
       <c r="AU7" s="4" t="inlineStr"/>
       <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW7" s="4" t="inlineStr"/>
       <c r="AX7" s="4" t="inlineStr"/>
       <c r="AY7" s="4" t="inlineStr"/>
       <c r="AZ7" s="4" t="inlineStr"/>
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -6180,17 +6380,13 @@
       <c r="BD7" s="4" t="inlineStr"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr"/>
       <c r="BG7" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
@@ -6207,756 +6403,8 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Corteva reaches FTC antitrust settlement, agrees to $35M payment (CTVA:NYSE)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOeC1lYkd1aElyM2QwcHpnR3l3Q2x1ODM2eW5pOUswcHNKTElxMWV5azFYTFhFUThLemhmdTNjcHdZRWxHTkthNlExOGN1NXFWaWtkZkxfNnZSaF8yZ0luRm1TT1hZSGJuNXlBaDlKS0JRTnAxYWRkdFlxWDRVWmROQXhNN3BaYk9QNklkbDR0NkRjamVJTVRwbzNIR05nN0tVeHc?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr">
-        <is>
-          <t>67911ce819d3444591d6976b52d3134f</t>
-        </is>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>4b033dbf29afc311be67812a</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>add022a25ab732e3141ba5e8</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Corteva, Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>States, FTC secure settlement in suit against Corteva pesticide loyalty programs</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPUm1sNG5vQTRqbEkwMmdWb3FTVWFWTDJ5dmpPTkZsakZYOUxfQklJWC1ZbDV3eVFHTGpuQkF1ZU12d0VxMkJnZ2FWZkNTN0FnQ0pVT09aNkhOYTFaYTBJcWl0Q1FMRmJDbDNGMlZuTE9iZnlOSkNrS2JIQ1dtd2lJaFFBaHcxWi15NkgydmlYQjFiMk5uaUJtVDBuRWNxYmY2MWVhLXJwQy1ENmVrM2d6bHRzcU80THBYWU1kbXdCaDQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>Iowa Capital Dispatch</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>2aacab99b13e4da492dd8f89a9d0ccb6</t>
-        </is>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
-        <is>
-          <t>fa55d6f911a75d41e6f1ed9e</t>
-        </is>
-      </c>
-      <c r="AD9" s="4" t="inlineStr">
-        <is>
-          <t>ef1fdace1b4d4ef928a14b4d</t>
-        </is>
-      </c>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP9" s="4" t="inlineStr"/>
-      <c r="AQ9" s="4" t="inlineStr"/>
-      <c r="AR9" s="4" t="inlineStr"/>
-      <c r="AS9" s="4" t="inlineStr"/>
-      <c r="AT9" s="4" t="inlineStr"/>
-      <c r="AU9" s="4" t="inlineStr"/>
-      <c r="AV9" s="4" t="inlineStr"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="inlineStr"/>
-      <c r="AY9" s="4" t="inlineStr"/>
-      <c r="AZ9" s="4" t="inlineStr"/>
-      <c r="BA9" s="4" t="inlineStr"/>
-      <c r="BB9" s="4" t="inlineStr">
-        <is>
-          <t>CTVA</t>
-        </is>
-      </c>
-      <c r="BC9" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="4" t="inlineStr"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="4" t="inlineStr"/>
-      <c r="BI9" s="4" t="inlineStr"/>
-      <c r="BJ9" s="4" t="inlineStr"/>
-      <c r="BK9" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Darden Restaurants (DRI) Stock May Be 13% Undervalued After Q1 Earnings Miss</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.824</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaXdua1JwcHFmRjRLZzV5NTBBcFhtQ280UERYQ3Z2Ul8zNUw3cVlqTWhhU2JOVHNJbS1pSFBwRDFMdklOSUJTSldCUTZDckZiQ2dnSEVzdnRmMVVmcVZLR0xfQXVLRUxLdXlUcl9PZHRpYTZtaDhRMExmRENzdHNLai1keDJaektNR01VTHZqT3REcVQzQkt5UllINVp3UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>b601ce027011be46f62ff559</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>260bef3068ad46f360e48c7b</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>DRI</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PNR DEADLINE NOTICE: Faruqi &amp; Faruqi, LLP Reminds Pentair (PNR) Investors of Securities Class Action Lawsuit Deadline on October 2, 2026</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxPZXA3WHpJeWVsMUQtTmY4bFpGaHZJZG5nbkh3LU5rQ2NxYkJ5a1Q3empxaEtSaWtkSW4zRnVEejAybldxZm5NWndPMnhvNXBoQ1RncFNpa3UzRHEzZUl4NG5ab2xRUW1ZOEo4NjJtdXNwb3JOSldfc0IyYnJTZUt3NkpJbW9ueW9SaE5JYkdSVDBPTEl6bTZraEVadW5HNU1tNmFNNEZiZ0pzYVo5d0RURW9NeG9rZUF3UHdQLXFWREg4ckdmaTkwVkt2WXVoYTI0Y0RZTS1veGxCZktDOTMzT3RiYzE5LTYxZU92eXBEclBpLW5HRWlvVlZrU3B3YmFfOW0wUWJITldESGdCaUw1WTZsaVhrTFVRaWc?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>f1d55caddc654688b58c6fb579b28c84</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>e219e320bea4f382169bc711</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>3b46f49745e60c6b38e6f5c0</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL11"/>
+  <autoFilter ref="A1:BL7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7943,645 +7391,645 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H2" s="3" t="b">
+      <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:23:38.366332+08:00</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T08:40:53.776257+08:00</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="P2" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1976</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="R2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" s="2" t="n">
         <v>1961</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="W2" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-25</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H3" s="3" t="b">
+      <c r="H3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:23:17.137147+08:00</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T08:40:12.120180+08:00</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="2" t="n">
         <v>2032</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2089</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="2" t="n">
         <v>2067</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>daily-2026-10-24</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>schedule</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H4" s="3" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:44:09.884829+08:00</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T13:04:34.984103+08:00</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="2" t="n">
         <v>3760</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>3802</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="2" t="n">
         <v>3825</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="2" t="n">
         <v>3793</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ticker-audit</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296780+08:00</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T08:15:49.296790+08:00</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="n">
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
         <v>1691</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="n">
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="b">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H7" s="3" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="P7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:16:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>方法一|方法二</t>
         </is>
       </c>
-      <c r="H8" s="3" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O8" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AA8"/>

--- a/news_daily/2026-09-28.xlsx
+++ b/news_daily/2026-09-28.xlsx
@@ -4182,28 +4182,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4243,7 +4247,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4252,7 +4256,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>e4ecfce542484932978e175befca2694</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
@@ -4273,7 +4281,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4317,10 +4329,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4356,28 +4380,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4417,7 +4445,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4426,7 +4454,11 @@
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr"/>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>edfec66ed36b4449b6584282b85ebda5</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>d8836955ecd1ed7c64c83def</t>
@@ -4447,7 +4479,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4491,10 +4527,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4530,28 +4578,32 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4591,7 +4643,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -4600,7 +4652,11 @@
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr"/>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>bcae0e8612204119b917bbdef12f4cf7</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>6a579d562e1dd94bd12fb056</t>
@@ -4621,7 +4677,11 @@
       <c r="AL21" s="2" t="inlineStr"/>
       <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="inlineStr"/>
-      <c r="AO21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="2" t="inlineStr"/>
       <c r="AQ21" s="2" t="inlineStr"/>
       <c r="AR21" s="2" t="inlineStr"/>
@@ -4665,10 +4725,22 @@
         </is>
       </c>
       <c r="BH21" s="2" t="inlineStr"/>
-      <c r="BI21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="2" t="inlineStr"/>
-      <c r="BK21" s="2" t="inlineStr"/>
-      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4704,28 +4776,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4765,7 +4841,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4774,7 +4850,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>d2bf64dc4fbf429e8cdef6ea4202b62c</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>108aa798b9a0975fcceb67db</t>
@@ -4795,7 +4875,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4839,10 +4923,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL22"/>
